--- a/tams-invest-parent/tams-invest-trade/src/main/resources/tpl/TrdPlanNetInvestTrade.xlsx
+++ b/tams-invest-parent/tams-invest-trade/src/main/resources/tpl/TrdPlanNetInvestTrade.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="22827"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\01.JOYINPROJECT\16.BSZCP\TisCode\2.1.2.2MS\tams-invest-parent\tams-invest-trade\src\main\resources\tpl\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workSpaceZhu\tams-invest-parent\tams-invest-trade\src\main\resources\tpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B103F7AC-5655-4F84-B70B-24D5F3456518}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="12720"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
   <si>
     <t>组合代码</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -79,25 +78,29 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>资产二级类型</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>资产三级类型</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>资产四级类型</t>
+    <t>资产二级分类</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>资产三级分类</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>资产四级分类</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>确认日期</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <numFmts count="2">
     <numFmt numFmtId="176" formatCode="#,##0.00_);\(#,##0.00\)"/>
-    <numFmt numFmtId="178" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd;@"/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -144,7 +147,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -157,19 +160,10 @@
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -451,28 +445,28 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:Q1"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
-    <col min="2" max="2" width="20.6640625" customWidth="1"/>
-    <col min="3" max="3" width="12.77734375" customWidth="1"/>
+    <col min="2" max="2" width="20.6328125" customWidth="1"/>
+    <col min="3" max="3" width="12.81640625" customWidth="1"/>
     <col min="4" max="4" width="17" customWidth="1"/>
-    <col min="5" max="5" width="17.88671875" customWidth="1"/>
-    <col min="6" max="6" width="16.6640625" customWidth="1"/>
-    <col min="7" max="7" width="16.77734375" customWidth="1"/>
-    <col min="8" max="10" width="13.109375" customWidth="1"/>
+    <col min="5" max="5" width="17.90625" customWidth="1"/>
+    <col min="6" max="6" width="16.6328125" customWidth="1"/>
+    <col min="7" max="7" width="16.81640625" customWidth="1"/>
+    <col min="8" max="10" width="13.08984375" customWidth="1"/>
     <col min="11" max="11" width="13" customWidth="1"/>
-    <col min="12" max="12" width="26.6640625" style="8" customWidth="1"/>
-    <col min="13" max="13" width="29.109375" style="3" customWidth="1"/>
-    <col min="14" max="14" width="27.6640625" style="3" customWidth="1"/>
-    <col min="15" max="15" width="12.88671875" customWidth="1"/>
-    <col min="16" max="16" width="57.21875" customWidth="1"/>
-    <col min="17" max="17" width="23.77734375" customWidth="1"/>
+    <col min="12" max="13" width="26.6328125" style="5" customWidth="1"/>
+    <col min="14" max="14" width="29.08984375" style="3" customWidth="1"/>
+    <col min="15" max="15" width="27.6328125" style="3" customWidth="1"/>
+    <col min="16" max="16" width="12.90625" customWidth="1"/>
+    <col min="17" max="17" width="57.1796875" customWidth="1"/>
+    <col min="18" max="18" width="23.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:17" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>5</v>
       </c>
@@ -506,29 +500,28 @@
       <c r="K1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="L1" s="6" t="s">
+      <c r="L1" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="M1" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="N1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="O1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:16" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="L2" s="7"/>
-      <c r="M2" s="5"/>
-      <c r="N2" s="5"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>